--- a/docs/workbook-split/dateien/GuV.xlsx
+++ b/docs/workbook-split/dateien/GuV.xlsx
@@ -726,62 +726,42 @@
           <t>Umsatzerlöse</t>
         </is>
       </c>
-      <c r="D7" s="6">
-        <f>SUMIFS(F7:Q7,$F$5:$Q$5,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E7" s="7">
-        <f>IF($D$9=0,"n.a.",D7/$D$9)</f>
-        <v/>
-      </c>
-      <c r="F7" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,1)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$E$7:$E$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,1),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,F$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,F$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,10)))</f>
-        <v/>
-      </c>
-      <c r="G7" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,2)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$E$7:$E$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,2),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,G$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,G$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,10)))</f>
-        <v/>
-      </c>
-      <c r="H7" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,3)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$E$7:$E$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,3),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,H$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,H$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,10)))</f>
-        <v/>
-      </c>
-      <c r="I7" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,4)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$E$7:$E$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,4),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,I$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,I$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,10)))</f>
-        <v/>
-      </c>
-      <c r="J7" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,5)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$E$7:$E$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,5),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,J$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,J$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,10)))</f>
-        <v/>
-      </c>
-      <c r="K7" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,6)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$E$7:$E$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,6),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,K$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,K$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,10)))</f>
-        <v/>
-      </c>
-      <c r="L7" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,7)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$E$7:$E$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,7),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,L$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,L$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,10)))</f>
-        <v/>
-      </c>
-      <c r="M7" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,8)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$E$7:$E$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,8),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,M$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,M$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,10)))</f>
-        <v/>
-      </c>
-      <c r="N7" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,9)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$E$7:$E$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,9),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,N$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,N$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,10)))</f>
-        <v/>
-      </c>
-      <c r="O7" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,10)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$E$7:$E$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,10),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,O$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,O$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,10)))</f>
-        <v/>
-      </c>
-      <c r="P7" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,11)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$E$7:$E$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,11),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,P$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,P$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,10)))</f>
-        <v/>
-      </c>
-      <c r="Q7" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,12)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$E$7:$E$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,12),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,Q$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,Q$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,10)))</f>
-        <v/>
-      </c>
+      <c r="D7" s="6" t="n">
+        <v>12189973.4</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>0.7129132259205198</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>639565.45</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>2777244.65</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1213541.38</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>678343.59</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>1347585.48</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>2470042.1</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>1323928.2</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>854339.84</v>
+      </c>
+      <c r="N7" s="6" t="n">
+        <v>885382.71</v>
+      </c>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
       <c r="R7" s="1" t="n"/>
     </row>
     <row r="8">
@@ -792,62 +772,42 @@
           <t>Bestandsveränderungen</t>
         </is>
       </c>
-      <c r="D8" s="6">
-        <f>SUMIFS(F8:Q8,$F$5:$Q$5,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E8" s="7">
-        <f>IF($D$9=0,"n.a.",D8/$D$9)</f>
-        <v/>
-      </c>
-      <c r="F8" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,1)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$F$7:$F$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,1),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,F$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,F$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,20)))</f>
-        <v/>
-      </c>
-      <c r="G8" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,2)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$F$7:$F$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,2),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,G$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,G$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,20)))</f>
-        <v/>
-      </c>
-      <c r="H8" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,3)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$F$7:$F$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,3),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,H$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,H$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,20)))</f>
-        <v/>
-      </c>
-      <c r="I8" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,4)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$F$7:$F$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,4),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,I$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,I$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,20)))</f>
-        <v/>
-      </c>
-      <c r="J8" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,5)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$F$7:$F$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,5),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,J$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,J$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,20)))</f>
-        <v/>
-      </c>
-      <c r="K8" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,6)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$F$7:$F$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,6),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,K$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,K$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,20)))</f>
-        <v/>
-      </c>
-      <c r="L8" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,7)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$F$7:$F$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,7),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,L$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,L$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,20)))</f>
-        <v/>
-      </c>
-      <c r="M8" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,8)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$F$7:$F$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,8),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,M$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,M$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,20)))</f>
-        <v/>
-      </c>
-      <c r="N8" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,9)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$F$7:$F$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,9),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,N$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,N$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,20)))</f>
-        <v/>
-      </c>
-      <c r="O8" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,10)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$F$7:$F$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,10),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,O$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,O$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,20)))</f>
-        <v/>
-      </c>
-      <c r="P8" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,11)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$F$7:$F$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,11),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,P$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,P$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,20)))</f>
-        <v/>
-      </c>
-      <c r="Q8" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,12)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$F$7:$F$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,12),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,Q$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,Q$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,20)))</f>
-        <v/>
-      </c>
+      <c r="D8" s="6" t="n">
+        <v>4908844.46</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>0.2870867740794801</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>1280847.26</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-200176.92</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1198671.49</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>1261219.89</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-263604.09</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>314645.23</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>294716.46</v>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>1022525.14</v>
+      </c>
+      <c r="N8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="6" t="n"/>
+      <c r="P8" s="6" t="n"/>
+      <c r="Q8" s="6" t="n"/>
       <c r="R8" s="1" t="n"/>
     </row>
     <row r="9" ht="25" customHeight="1">
@@ -858,62 +818,42 @@
           <t>Gesamtleistung</t>
         </is>
       </c>
-      <c r="D9" s="9">
-        <f>SUMIFS(F9:Q9,$F$5:$Q$5,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E9" s="10">
-        <f>IF($D$9=0,"n.a.",D9/$D$9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="9">
-        <f>IF(F7="","",SUM(F7:F8))</f>
-        <v/>
-      </c>
-      <c r="G9" s="9">
-        <f>IF(G7="","",SUM(G7:G8))</f>
-        <v/>
-      </c>
-      <c r="H9" s="9">
-        <f>IF(H7="","",SUM(H7:H8))</f>
-        <v/>
-      </c>
-      <c r="I9" s="9">
-        <f>IF(I7="","",SUM(I7:I8))</f>
-        <v/>
-      </c>
-      <c r="J9" s="9">
-        <f>IF(J7="","",SUM(J7:J8))</f>
-        <v/>
-      </c>
-      <c r="K9" s="9">
-        <f>IF(K7="","",SUM(K7:K8))</f>
-        <v/>
-      </c>
-      <c r="L9" s="9">
-        <f>IF(L7="","",SUM(L7:L8))</f>
-        <v/>
-      </c>
-      <c r="M9" s="9">
-        <f>IF(M7="","",SUM(M7:M8))</f>
-        <v/>
-      </c>
-      <c r="N9" s="9">
-        <f>IF(N7="","",SUM(N7:N8))</f>
-        <v/>
-      </c>
-      <c r="O9" s="9">
-        <f>IF(O7="","",SUM(O7:O8))</f>
-        <v/>
-      </c>
-      <c r="P9" s="9">
-        <f>IF(P7="","",SUM(P7:P8))</f>
-        <v/>
-      </c>
-      <c r="Q9" s="9">
-        <f>IF(Q7="","",SUM(Q7:Q8))</f>
-        <v/>
-      </c>
+      <c r="D9" s="9" t="n">
+        <v>17098817.86</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>1920412.71</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>2577067.73</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>2412212.87</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>1939563.48</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>1083981.39</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>2784687.33</v>
+      </c>
+      <c r="L9" s="9" t="n">
+        <v>1618644.66</v>
+      </c>
+      <c r="M9" s="9" t="n">
+        <v>1876864.98</v>
+      </c>
+      <c r="N9" s="9" t="n">
+        <v>885382.71</v>
+      </c>
+      <c r="O9" s="9" t="n"/>
+      <c r="P9" s="9" t="n"/>
+      <c r="Q9" s="9" t="n"/>
       <c r="R9" s="1" t="n"/>
     </row>
     <row r="10">
@@ -924,62 +864,42 @@
           <t>Sonstige betriebliche Erträge</t>
         </is>
       </c>
-      <c r="D10" s="6">
-        <f>SUMIFS(F10:Q10,$F$5:$Q$5,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E10" s="7">
-        <f>IF($D$9=0,"n.a.",D10/$D$9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,1)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$G$7:$G$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,1),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,F$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,F$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,30)))</f>
-        <v/>
-      </c>
-      <c r="G10" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,2)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$G$7:$G$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,2),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,G$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,G$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,30)))</f>
-        <v/>
-      </c>
-      <c r="H10" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,3)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$G$7:$G$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,3),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,H$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,H$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,30)))</f>
-        <v/>
-      </c>
-      <c r="I10" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,4)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$G$7:$G$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,4),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,I$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,I$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,30)))</f>
-        <v/>
-      </c>
-      <c r="J10" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,5)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$G$7:$G$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,5),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,J$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,J$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,30)))</f>
-        <v/>
-      </c>
-      <c r="K10" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,6)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$G$7:$G$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,6),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,K$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,K$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,30)))</f>
-        <v/>
-      </c>
-      <c r="L10" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,7)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$G$7:$G$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,7),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,L$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,L$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,30)))</f>
-        <v/>
-      </c>
-      <c r="M10" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,8)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$G$7:$G$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,8),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,M$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,M$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,30)))</f>
-        <v/>
-      </c>
-      <c r="N10" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,9)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$G$7:$G$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,9),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,N$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,N$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,30)))</f>
-        <v/>
-      </c>
-      <c r="O10" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,10)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$G$7:$G$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,10),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,O$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,O$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,30)))</f>
-        <v/>
-      </c>
-      <c r="P10" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,11)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$G$7:$G$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,11),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,P$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,P$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,30)))</f>
-        <v/>
-      </c>
-      <c r="Q10" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,12)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$G$7:$G$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,12),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,Q$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,Q$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,30)))</f>
-        <v/>
-      </c>
+      <c r="D10" s="6" t="n">
+        <v>502291.14</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>0.02937578165418273</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>12030.21</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>22190.76</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>15409.39</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>56063.55</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>24678.87</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>17068.34</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>15326.23</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>14281.36</v>
+      </c>
+      <c r="N10" s="6" t="n">
+        <v>325242.43</v>
+      </c>
+      <c r="O10" s="6" t="n"/>
+      <c r="P10" s="6" t="n"/>
+      <c r="Q10" s="6" t="n"/>
       <c r="R10" s="1" t="n"/>
     </row>
     <row r="11">
@@ -990,62 +910,42 @@
           <t>Materialaufwand</t>
         </is>
       </c>
-      <c r="D11" s="6">
-        <f>SUMIFS(F11:Q11,$F$5:$Q$5,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E11" s="7">
-        <f>IF($D$9=0,"n.a.",D11/$D$9)</f>
-        <v/>
-      </c>
-      <c r="F11" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,1)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$H$7:$H$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,1),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,F$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,F$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,40)))</f>
-        <v/>
-      </c>
-      <c r="G11" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,2)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$H$7:$H$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,2),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,G$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,G$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,40)))</f>
-        <v/>
-      </c>
-      <c r="H11" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,3)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$H$7:$H$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,3),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,H$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,H$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,40)))</f>
-        <v/>
-      </c>
-      <c r="I11" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,4)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$H$7:$H$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,4),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,I$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,I$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,40)))</f>
-        <v/>
-      </c>
-      <c r="J11" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,5)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$H$7:$H$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,5),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,J$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,J$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,40)))</f>
-        <v/>
-      </c>
-      <c r="K11" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,6)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$H$7:$H$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,6),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,K$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,K$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,40)))</f>
-        <v/>
-      </c>
-      <c r="L11" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,7)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$H$7:$H$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,7),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,L$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,L$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,40)))</f>
-        <v/>
-      </c>
-      <c r="M11" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,8)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$H$7:$H$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,8),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,M$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,M$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,40)))</f>
-        <v/>
-      </c>
-      <c r="N11" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,9)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$H$7:$H$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,9),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,N$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,N$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,40)))</f>
-        <v/>
-      </c>
-      <c r="O11" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,10)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$H$7:$H$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,10),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,O$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,O$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,40)))</f>
-        <v/>
-      </c>
-      <c r="P11" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,11)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$H$7:$H$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,11),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,P$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,P$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,40)))</f>
-        <v/>
-      </c>
-      <c r="Q11" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,12)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$H$7:$H$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,12),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,Q$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,Q$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,40)))</f>
-        <v/>
-      </c>
+      <c r="D11" s="6" t="n">
+        <v>-13430817.92</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>-0.7854822497068228</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-1080421</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-1706242.27</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-1746548.03</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-1520583.11</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-582901.1800000001</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>-2109049.83</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>-1512452.36</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>-1436882.3</v>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>-1735737.84</v>
+      </c>
+      <c r="O11" s="6" t="n"/>
+      <c r="P11" s="6" t="n"/>
+      <c r="Q11" s="6" t="n"/>
       <c r="R11" s="1" t="n"/>
     </row>
     <row r="12">
@@ -1056,62 +956,42 @@
           <t>Personalaufwand</t>
         </is>
       </c>
-      <c r="D12" s="6">
-        <f>SUMIFS(F12:Q12,$F$5:$Q$5,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E12" s="7">
-        <f>IF($D$9=0,"n.a.",D12/$D$9)</f>
-        <v/>
-      </c>
-      <c r="F12" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,1)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$I$7:$I$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,1),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,F$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,F$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,50)))</f>
-        <v/>
-      </c>
-      <c r="G12" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,2)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$I$7:$I$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,2),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,G$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,G$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,50)))</f>
-        <v/>
-      </c>
-      <c r="H12" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,3)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$I$7:$I$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,3),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,H$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,H$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,50)))</f>
-        <v/>
-      </c>
-      <c r="I12" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,4)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$I$7:$I$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,4),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,I$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,I$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,50)))</f>
-        <v/>
-      </c>
-      <c r="J12" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,5)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$I$7:$I$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,5),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,J$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,J$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,50)))</f>
-        <v/>
-      </c>
-      <c r="K12" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,6)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$I$7:$I$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,6),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,K$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,K$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,50)))</f>
-        <v/>
-      </c>
-      <c r="L12" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,7)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$I$7:$I$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,7),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,L$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,L$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,50)))</f>
-        <v/>
-      </c>
-      <c r="M12" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,8)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$I$7:$I$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,8),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,M$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,M$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,50)))</f>
-        <v/>
-      </c>
-      <c r="N12" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,9)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$I$7:$I$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,9),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,N$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,N$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,50)))</f>
-        <v/>
-      </c>
-      <c r="O12" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,10)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$I$7:$I$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,10),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,O$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,O$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,50)))</f>
-        <v/>
-      </c>
-      <c r="P12" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,11)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$I$7:$I$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,11),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,P$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,P$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,50)))</f>
-        <v/>
-      </c>
-      <c r="Q12" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,12)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$I$7:$I$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,12),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,Q$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,Q$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,50)))</f>
-        <v/>
-      </c>
+      <c r="D12" s="6" t="n">
+        <v>-3427005.18</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>-0.2004235151259749</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>-338608.8</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>-363244</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>-383792.43</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>-383705.5</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>-432453.34</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>-378900.06</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>-390395</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>-399129.54</v>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>-356776.51</v>
+      </c>
+      <c r="O12" s="6" t="n"/>
+      <c r="P12" s="6" t="n"/>
+      <c r="Q12" s="6" t="n"/>
       <c r="R12" s="1" t="n"/>
     </row>
     <row r="13">
@@ -1122,62 +1002,42 @@
           <t>Sonstige betriebliche Aufwendungen</t>
         </is>
       </c>
-      <c r="D13" s="6">
-        <f>SUMIFS(F13:Q13,$F$5:$Q$5,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E13" s="7">
-        <f>IF($D$9=0,"n.a.",D13/$D$9)</f>
-        <v/>
-      </c>
-      <c r="F13" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,1)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$J$7:$J$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,1),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,F$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,F$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,70)))</f>
-        <v/>
-      </c>
-      <c r="G13" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,2)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$J$7:$J$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,2),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,G$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,G$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,70)))</f>
-        <v/>
-      </c>
-      <c r="H13" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,3)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$J$7:$J$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,3),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,H$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,H$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,70)))</f>
-        <v/>
-      </c>
-      <c r="I13" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,4)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$J$7:$J$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,4),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,I$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,I$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,70)))</f>
-        <v/>
-      </c>
-      <c r="J13" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,5)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$J$7:$J$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,5),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,J$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,J$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,70)))</f>
-        <v/>
-      </c>
-      <c r="K13" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,6)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$J$7:$J$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,6),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,K$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,K$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,70)))</f>
-        <v/>
-      </c>
-      <c r="L13" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,7)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$J$7:$J$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,7),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,L$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,L$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,70)))</f>
-        <v/>
-      </c>
-      <c r="M13" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,8)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$J$7:$J$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,8),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,M$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,M$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,70)))</f>
-        <v/>
-      </c>
-      <c r="N13" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,9)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$J$7:$J$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,9),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,N$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,N$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,70)))</f>
-        <v/>
-      </c>
-      <c r="O13" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,10)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$J$7:$J$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,10),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,O$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,O$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,70)))</f>
-        <v/>
-      </c>
-      <c r="P13" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,11)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$J$7:$J$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,11),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,P$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,P$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,70)))</f>
-        <v/>
-      </c>
-      <c r="Q13" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,12)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$J$7:$J$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,12),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,Q$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,Q$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,70)))</f>
-        <v/>
-      </c>
+      <c r="D13" s="6" t="n">
+        <v>-2188667.93</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>-0.1280011254532423</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-223180.95</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-214918.93</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-286856.5</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-275785.95</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-237116.93</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>-255251.92</v>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>-245246.07</v>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>-191884.67</v>
+      </c>
+      <c r="N13" s="6" t="n">
+        <v>-258426.01</v>
+      </c>
+      <c r="O13" s="6" t="n"/>
+      <c r="P13" s="6" t="n"/>
+      <c r="Q13" s="6" t="n"/>
       <c r="R13" s="1" t="n"/>
     </row>
     <row r="14" ht="25" customHeight="1">
@@ -1188,62 +1048,42 @@
           <t>EBITDA aus Staffel</t>
         </is>
       </c>
-      <c r="D14" s="9">
-        <f>SUMIFS(F14:Q14,$F$5:$Q$5,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E14" s="10">
-        <f>IF($D$9=0,"n.a.",D14/$D$9)</f>
-        <v/>
-      </c>
-      <c r="F14" s="9">
-        <f>IF(F7="","",SUM(F9:F13))</f>
-        <v/>
-      </c>
-      <c r="G14" s="9">
-        <f>IF(G7="","",SUM(G9:G13))</f>
-        <v/>
-      </c>
-      <c r="H14" s="9">
-        <f>IF(H7="","",SUM(H9:H13))</f>
-        <v/>
-      </c>
-      <c r="I14" s="9">
-        <f>IF(I7="","",SUM(I9:I13))</f>
-        <v/>
-      </c>
-      <c r="J14" s="9">
-        <f>IF(J7="","",SUM(J9:J13))</f>
-        <v/>
-      </c>
-      <c r="K14" s="9">
-        <f>IF(K7="","",SUM(K9:K13))</f>
-        <v/>
-      </c>
-      <c r="L14" s="9">
-        <f>IF(L7="","",SUM(L9:L13))</f>
-        <v/>
-      </c>
-      <c r="M14" s="9">
-        <f>IF(M7="","",SUM(M9:M13))</f>
-        <v/>
-      </c>
-      <c r="N14" s="9">
-        <f>IF(N7="","",SUM(N9:N13))</f>
-        <v/>
-      </c>
-      <c r="O14" s="9">
-        <f>IF(O7="","",SUM(O9:O13))</f>
-        <v/>
-      </c>
-      <c r="P14" s="9">
-        <f>IF(P7="","",SUM(P9:P13))</f>
-        <v/>
-      </c>
-      <c r="Q14" s="9">
-        <f>IF(Q7="","",SUM(Q9:Q13))</f>
-        <v/>
-      </c>
+      <c r="D14" s="9" t="n">
+        <v>-1445382.030000001</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>-0.08453110863185724</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>290232.1699999999</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>314853.2899999997</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>10425.30000000022</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>-184447.5300000001</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>-143811.1900000001</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>58553.85999999984</v>
+      </c>
+      <c r="L14" s="9" t="n">
+        <v>-514122.5400000002</v>
+      </c>
+      <c r="M14" s="9" t="n">
+        <v>-136750.17</v>
+      </c>
+      <c r="N14" s="9" t="n">
+        <v>-1140315.22</v>
+      </c>
+      <c r="O14" s="9" t="n"/>
+      <c r="P14" s="9" t="n"/>
+      <c r="Q14" s="9" t="n"/>
       <c r="R14" s="1" t="n"/>
     </row>
     <row r="15">
@@ -1254,62 +1094,42 @@
           <t>Abschreibungen</t>
         </is>
       </c>
-      <c r="D15" s="6">
-        <f>SUMIFS(F15:Q15,$F$5:$Q$5,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E15" s="7">
-        <f>IF($D$9=0,"n.a.",D15/$D$9)</f>
-        <v/>
-      </c>
-      <c r="F15" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,1)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$K$7:$K$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,1),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,F$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,F$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,60)))</f>
-        <v/>
-      </c>
-      <c r="G15" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,2)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$K$7:$K$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,2),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,G$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,G$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,60)))</f>
-        <v/>
-      </c>
-      <c r="H15" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,3)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$K$7:$K$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,3),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,H$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,H$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,60)))</f>
-        <v/>
-      </c>
-      <c r="I15" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,4)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$K$7:$K$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,4),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,I$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,I$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,60)))</f>
-        <v/>
-      </c>
-      <c r="J15" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,5)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$K$7:$K$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,5),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,J$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,J$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,60)))</f>
-        <v/>
-      </c>
-      <c r="K15" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,6)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$K$7:$K$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,6),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,K$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,K$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,60)))</f>
-        <v/>
-      </c>
-      <c r="L15" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,7)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$K$7:$K$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,7),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,L$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,L$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,60)))</f>
-        <v/>
-      </c>
-      <c r="M15" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,8)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$K$7:$K$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,8),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,M$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,M$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,60)))</f>
-        <v/>
-      </c>
-      <c r="N15" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,9)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$K$7:$K$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,9),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,N$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,N$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,60)))</f>
-        <v/>
-      </c>
-      <c r="O15" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,10)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$K$7:$K$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,10),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,O$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,O$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,60)))</f>
-        <v/>
-      </c>
-      <c r="P15" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,11)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$K$7:$K$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,11),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,P$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,P$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,60)))</f>
-        <v/>
-      </c>
-      <c r="Q15" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,12)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$K$7:$K$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,12),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,Q$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,Q$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,60)))</f>
-        <v/>
-      </c>
+      <c r="D15" s="6" t="n">
+        <v>-84778.77</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>-0.004958165569932564</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-9645.450000000001</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-9711.51</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-9824.139999999999</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>-9599.860000000001</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>-9655.030000000001</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>-9047.959999999999</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>-9082.969999999999</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>-9109.85</v>
+      </c>
+      <c r="N15" s="6" t="n">
+        <v>-9102</v>
+      </c>
+      <c r="O15" s="6" t="n"/>
+      <c r="P15" s="6" t="n"/>
+      <c r="Q15" s="6" t="n"/>
       <c r="R15" s="1" t="n"/>
     </row>
     <row r="16" ht="25" customHeight="1">
@@ -1320,62 +1140,42 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="D16" s="9">
-        <f>SUMIFS(F16:Q16,$F$5:$Q$5,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E16" s="10">
-        <f>IF($D$9=0,"n.a.",D16/$D$9)</f>
-        <v/>
-      </c>
-      <c r="F16" s="9">
-        <f>IF(F7="","",SUM(F14:F15))</f>
-        <v/>
-      </c>
-      <c r="G16" s="9">
-        <f>IF(G7="","",SUM(G14:G15))</f>
-        <v/>
-      </c>
-      <c r="H16" s="9">
-        <f>IF(H7="","",SUM(H14:H15))</f>
-        <v/>
-      </c>
-      <c r="I16" s="9">
-        <f>IF(I7="","",SUM(I14:I15))</f>
-        <v/>
-      </c>
-      <c r="J16" s="9">
-        <f>IF(J7="","",SUM(J14:J15))</f>
-        <v/>
-      </c>
-      <c r="K16" s="9">
-        <f>IF(K7="","",SUM(K14:K15))</f>
-        <v/>
-      </c>
-      <c r="L16" s="9">
-        <f>IF(L7="","",SUM(L14:L15))</f>
-        <v/>
-      </c>
-      <c r="M16" s="9">
-        <f>IF(M7="","",SUM(M14:M15))</f>
-        <v/>
-      </c>
-      <c r="N16" s="9">
-        <f>IF(N7="","",SUM(N14:N15))</f>
-        <v/>
-      </c>
-      <c r="O16" s="9">
-        <f>IF(O7="","",SUM(O14:O15))</f>
-        <v/>
-      </c>
-      <c r="P16" s="9">
-        <f>IF(P7="","",SUM(P14:P15))</f>
-        <v/>
-      </c>
-      <c r="Q16" s="9">
-        <f>IF(Q7="","",SUM(Q14:Q15))</f>
-        <v/>
-      </c>
+      <c r="D16" s="9" t="n">
+        <v>-1530160.800000001</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>-0.0894892742017898</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>280586.7199999999</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>305141.7799999997</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>601.1600000002218</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>-194047.3900000001</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>-153466.2200000001</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>49505.89999999984</v>
+      </c>
+      <c r="L16" s="9" t="n">
+        <v>-523205.5100000002</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>-145860.02</v>
+      </c>
+      <c r="N16" s="9" t="n">
+        <v>-1149417.22</v>
+      </c>
+      <c r="O16" s="9" t="n"/>
+      <c r="P16" s="9" t="n"/>
+      <c r="Q16" s="9" t="n"/>
       <c r="R16" s="1" t="n"/>
     </row>
     <row r="17">
@@ -1386,62 +1186,42 @@
           <t>Finanzergebnis</t>
         </is>
       </c>
-      <c r="D17" s="6">
-        <f>SUMIFS(F17:Q17,$F$5:$Q$5,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E17" s="7">
-        <f>IF($D$9=0,"n.a.",D17/$D$9)</f>
-        <v/>
-      </c>
-      <c r="F17" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,1)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$L$7:$L$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,1),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,F$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,F$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,80)))</f>
-        <v/>
-      </c>
-      <c r="G17" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,2)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$L$7:$L$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,2),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,G$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,G$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,80)))</f>
-        <v/>
-      </c>
-      <c r="H17" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,3)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$L$7:$L$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,3),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,H$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,H$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,80)))</f>
-        <v/>
-      </c>
-      <c r="I17" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,4)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$L$7:$L$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,4),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,I$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,I$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,80)))</f>
-        <v/>
-      </c>
-      <c r="J17" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,5)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$L$7:$L$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,5),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,J$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,J$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,80)))</f>
-        <v/>
-      </c>
-      <c r="K17" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,6)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$L$7:$L$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,6),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,K$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,K$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,80)))</f>
-        <v/>
-      </c>
-      <c r="L17" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,7)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$L$7:$L$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,7),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,L$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,L$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,80)))</f>
-        <v/>
-      </c>
-      <c r="M17" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,8)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$L$7:$L$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,8),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,M$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,M$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,80)))</f>
-        <v/>
-      </c>
-      <c r="N17" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,9)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$L$7:$L$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,9),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,N$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,N$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,80)))</f>
-        <v/>
-      </c>
-      <c r="O17" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,10)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$L$7:$L$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,10),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,O$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,O$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,80)))</f>
-        <v/>
-      </c>
-      <c r="P17" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,11)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$L$7:$L$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,11),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,P$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,P$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,80)))</f>
-        <v/>
-      </c>
-      <c r="Q17" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,12)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$L$7:$L$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,12),IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,Q$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$45:$E$115,'[D Finanzen.xlsx]D Finanzen'!$A$45:$A$115,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$45:$B$115,Q$5,'[D Finanzen.xlsx]D Finanzen'!$C$45:$C$115,80)))</f>
-        <v/>
-      </c>
+      <c r="D17" s="6" t="n">
+        <v>-71521.75</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>-0.004182847643948177</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-5854.47</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-6903.55</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-9432.18</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-8779.92</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-15584.75</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>-12828.32</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>-8079.09</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>-12425.47</v>
+      </c>
+      <c r="N17" s="6" t="n">
+        <v>8366</v>
+      </c>
+      <c r="O17" s="6" t="n"/>
+      <c r="P17" s="6" t="n"/>
+      <c r="Q17" s="6" t="n"/>
       <c r="R17" s="1" t="n"/>
     </row>
     <row r="18" ht="25" customHeight="1">
@@ -1452,62 +1232,42 @@
           <t>Ergebnis aus Staffel</t>
         </is>
       </c>
-      <c r="D18" s="9">
-        <f>SUMIFS(F18:Q18,$F$5:$Q$5,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E18" s="10">
-        <f>IF($D$9=0,"n.a.",D18/$D$9)</f>
-        <v/>
-      </c>
-      <c r="F18" s="9">
-        <f>IF(F7="","",SUM(F16:F17))</f>
-        <v/>
-      </c>
-      <c r="G18" s="9">
-        <f>IF(G7="","",SUM(G16:G17))</f>
-        <v/>
-      </c>
-      <c r="H18" s="9">
-        <f>IF(H7="","",SUM(H16:H17))</f>
-        <v/>
-      </c>
-      <c r="I18" s="9">
-        <f>IF(I7="","",SUM(I16:I17))</f>
-        <v/>
-      </c>
-      <c r="J18" s="9">
-        <f>IF(J7="","",SUM(J16:J17))</f>
-        <v/>
-      </c>
-      <c r="K18" s="9">
-        <f>IF(K7="","",SUM(K16:K17))</f>
-        <v/>
-      </c>
-      <c r="L18" s="9">
-        <f>IF(L7="","",SUM(L16:L17))</f>
-        <v/>
-      </c>
-      <c r="M18" s="9">
-        <f>IF(M7="","",SUM(M16:M17))</f>
-        <v/>
-      </c>
-      <c r="N18" s="9">
-        <f>IF(N7="","",SUM(N16:N17))</f>
-        <v/>
-      </c>
-      <c r="O18" s="9">
-        <f>IF(O7="","",SUM(O16:O17))</f>
-        <v/>
-      </c>
-      <c r="P18" s="9">
-        <f>IF(P7="","",SUM(P16:P17))</f>
-        <v/>
-      </c>
-      <c r="Q18" s="9">
-        <f>IF(Q7="","",SUM(Q16:Q17))</f>
-        <v/>
-      </c>
+      <c r="D18" s="9" t="n">
+        <v>-1601682.550000001</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>-0.09367212184573799</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>274732.2499999999</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>298238.2299999997</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>-8831.019999999779</v>
+      </c>
+      <c r="I18" s="9" t="n">
+        <v>-202827.3100000001</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>-169050.9700000001</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>36677.57999999984</v>
+      </c>
+      <c r="L18" s="9" t="n">
+        <v>-531284.6000000002</v>
+      </c>
+      <c r="M18" s="9" t="n">
+        <v>-158285.49</v>
+      </c>
+      <c r="N18" s="9" t="n">
+        <v>-1141051.22</v>
+      </c>
+      <c r="O18" s="9" t="n"/>
+      <c r="P18" s="9" t="n"/>
+      <c r="Q18" s="9" t="n"/>
       <c r="R18" s="1" t="n"/>
     </row>
     <row r="19">
@@ -1538,62 +1298,42 @@
           <t>EBITDA Cockpit-Definition</t>
         </is>
       </c>
-      <c r="D20" s="9">
-        <f>SUMIFS(F20:Q20,$F$5:$Q$5,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E20" s="10">
-        <f>IF($D$9=0,"n.a.",D20/$D$9)</f>
-        <v/>
-      </c>
-      <c r="F20" s="9">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,1)&gt;0,F14,IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,F$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$8:$F$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,F$5)))</f>
-        <v/>
-      </c>
-      <c r="G20" s="9">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,2)&gt;0,G14,IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,G$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$8:$F$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,G$5)))</f>
-        <v/>
-      </c>
-      <c r="H20" s="9">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,3)&gt;0,H14,IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,H$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$8:$F$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,H$5)))</f>
-        <v/>
-      </c>
-      <c r="I20" s="9">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,4)&gt;0,I14,IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,I$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$8:$F$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,I$5)))</f>
-        <v/>
-      </c>
-      <c r="J20" s="9">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,5)&gt;0,J14,IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,J$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$8:$F$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,J$5)))</f>
-        <v/>
-      </c>
-      <c r="K20" s="9">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,6)&gt;0,K14,IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,K$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$8:$F$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,K$5)))</f>
-        <v/>
-      </c>
-      <c r="L20" s="9">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,7)&gt;0,L14,IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,L$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$8:$F$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,L$5)))</f>
-        <v/>
-      </c>
-      <c r="M20" s="9">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,8)&gt;0,M14,IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,M$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$8:$F$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,M$5)))</f>
-        <v/>
-      </c>
-      <c r="N20" s="9">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,9)&gt;0,N14,IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,N$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$8:$F$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,N$5)))</f>
-        <v/>
-      </c>
-      <c r="O20" s="9">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,10)&gt;0,O14,IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,O$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$8:$F$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,O$5)))</f>
-        <v/>
-      </c>
-      <c r="P20" s="9">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,11)&gt;0,P14,IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,P$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$8:$F$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,P$5)))</f>
-        <v/>
-      </c>
-      <c r="Q20" s="9">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,12)&gt;0,Q14,IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,Q$5)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$F$8:$F$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,Q$5)))</f>
-        <v/>
-      </c>
+      <c r="D20" s="9" t="n">
+        <v>-1711536.9</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>-0.1000967969840694</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>294942.37</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>318570.76</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>23595.18</v>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>-179274.07</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>-141241.9</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>58553.86</v>
+      </c>
+      <c r="L20" s="9" t="n">
+        <v>-495291.54</v>
+      </c>
+      <c r="M20" s="9" t="n">
+        <v>-138242.37</v>
+      </c>
+      <c r="N20" s="9" t="n">
+        <v>-1453149.19</v>
+      </c>
+      <c r="O20" s="9" t="n"/>
+      <c r="P20" s="9" t="n"/>
+      <c r="Q20" s="9" t="n"/>
       <c r="R20" s="1" t="n"/>
     </row>
     <row r="21">
@@ -1604,62 +1344,42 @@
           <t>Differenz EBITDA-Definition</t>
         </is>
       </c>
-      <c r="D21" s="6">
-        <f>SUMIFS(F21:Q21,$F$5:$Q$5,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E21" s="7">
-        <f>IF($D$9=0,"n.a.",D21/$D$9)</f>
-        <v/>
-      </c>
-      <c r="F21" s="6">
-        <f>IF(F7="","",ROUND(F14-F20,2))</f>
-        <v/>
-      </c>
-      <c r="G21" s="6">
-        <f>IF(G7="","",ROUND(G14-G20,2))</f>
-        <v/>
-      </c>
-      <c r="H21" s="6">
-        <f>IF(H7="","",ROUND(H14-H20,2))</f>
-        <v/>
-      </c>
-      <c r="I21" s="6">
-        <f>IF(I7="","",ROUND(I14-I20,2))</f>
-        <v/>
-      </c>
-      <c r="J21" s="6">
-        <f>IF(J7="","",ROUND(J14-J20,2))</f>
-        <v/>
-      </c>
-      <c r="K21" s="6">
-        <f>IF(K7="","",ROUND(K14-K20,2))</f>
-        <v/>
-      </c>
-      <c r="L21" s="6">
-        <f>IF(L7="","",ROUND(L14-L20,2))</f>
-        <v/>
-      </c>
-      <c r="M21" s="6">
-        <f>IF(M7="","",ROUND(M14-M20,2))</f>
-        <v/>
-      </c>
-      <c r="N21" s="6">
-        <f>IF(N7="","",ROUND(N14-N20,2))</f>
-        <v/>
-      </c>
-      <c r="O21" s="6">
-        <f>IF(O7="","",ROUND(O14-O20,2))</f>
-        <v/>
-      </c>
-      <c r="P21" s="6">
-        <f>IF(P7="","",ROUND(P14-P20,2))</f>
-        <v/>
-      </c>
-      <c r="Q21" s="6">
-        <f>IF(Q7="","",ROUND(Q14-Q20,2))</f>
-        <v/>
-      </c>
+      <c r="D21" s="6" t="n">
+        <v>266154.87</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>0.0155656883522122</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>-4710.2</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>-3717.47</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>-13169.88</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>-5173.46</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>-2569.29</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="6" t="n">
+        <v>-18831</v>
+      </c>
+      <c r="M21" s="6" t="n">
+        <v>1492.2</v>
+      </c>
+      <c r="N21" s="6" t="n">
+        <v>312833.97</v>
+      </c>
+      <c r="O21" s="6" t="n"/>
+      <c r="P21" s="6" t="n"/>
+      <c r="Q21" s="6" t="n"/>
       <c r="R21" s="1" t="n"/>
     </row>
     <row r="22">
@@ -1692,53 +1412,65 @@
       </c>
       <c r="D23" s="1" t="n"/>
       <c r="E23" s="1" t="n"/>
-      <c r="F23" s="1">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,1)&gt;0,"CSV-Import","Originalexport")</f>
-        <v/>
-      </c>
-      <c r="G23" s="1">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,2)&gt;0,"CSV-Import","Originalexport")</f>
-        <v/>
-      </c>
-      <c r="H23" s="1">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,3)&gt;0,"CSV-Import","Originalexport")</f>
-        <v/>
-      </c>
-      <c r="I23" s="1">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,4)&gt;0,"CSV-Import","Originalexport")</f>
-        <v/>
-      </c>
-      <c r="J23" s="1">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,5)&gt;0,"CSV-Import","Originalexport")</f>
-        <v/>
-      </c>
-      <c r="K23" s="1">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,6)&gt;0,"CSV-Import","Originalexport")</f>
-        <v/>
-      </c>
-      <c r="L23" s="1">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,7)&gt;0,"CSV-Import","Originalexport")</f>
-        <v/>
-      </c>
-      <c r="M23" s="1">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,8)&gt;0,"CSV-Import","Originalexport")</f>
-        <v/>
-      </c>
-      <c r="N23" s="1">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,9)&gt;0,"CSV-Import","Originalexport")</f>
-        <v/>
-      </c>
-      <c r="O23" s="1">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,10)&gt;0,"CSV-Import","Originalexport")</f>
-        <v/>
-      </c>
-      <c r="P23" s="1">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,11)&gt;0,"CSV-Import","Originalexport")</f>
-        <v/>
-      </c>
-      <c r="Q23" s="1">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,12)&gt;0,"CSV-Import","Originalexport")</f>
-        <v/>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>Originalexport</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>Originalexport</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="inlineStr">
+        <is>
+          <t>Originalexport</t>
+        </is>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>Originalexport</t>
+        </is>
+      </c>
+      <c r="J23" s="1" t="inlineStr">
+        <is>
+          <t>Originalexport</t>
+        </is>
+      </c>
+      <c r="K23" s="1" t="inlineStr">
+        <is>
+          <t>Originalexport</t>
+        </is>
+      </c>
+      <c r="L23" s="1" t="inlineStr">
+        <is>
+          <t>Originalexport</t>
+        </is>
+      </c>
+      <c r="M23" s="1" t="inlineStr">
+        <is>
+          <t>Originalexport</t>
+        </is>
+      </c>
+      <c r="N23" s="1" t="inlineStr">
+        <is>
+          <t>Originalexport</t>
+        </is>
+      </c>
+      <c r="O23" s="1" t="inlineStr">
+        <is>
+          <t>Originalexport</t>
+        </is>
+      </c>
+      <c r="P23" s="1" t="inlineStr">
+        <is>
+          <t>Originalexport</t>
+        </is>
+      </c>
+      <c r="Q23" s="1" t="inlineStr">
+        <is>
+          <t>Originalexport</t>
+        </is>
       </c>
       <c r="R23" s="1" t="n"/>
     </row>
@@ -1750,58 +1482,45 @@
           <t>Neutrales Ergebnis</t>
         </is>
       </c>
-      <c r="D24" s="6">
-        <f>SUMIFS(F24:Q24,$F$5:$Q$5,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
+      <c r="D24" s="6" t="n">
+        <v>265544.3199999999</v>
       </c>
       <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,1)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$M$7:$M$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,1),SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$8:$G$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,1))</f>
-        <v/>
-      </c>
-      <c r="G24" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,2)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$M$7:$M$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,2),SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$8:$G$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,2))</f>
-        <v/>
-      </c>
-      <c r="H24" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,3)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$M$7:$M$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,3),SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$8:$G$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,3))</f>
-        <v/>
-      </c>
-      <c r="I24" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,4)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$M$7:$M$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,4),SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$8:$G$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,4))</f>
-        <v/>
-      </c>
-      <c r="J24" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,5)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$M$7:$M$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,5),SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$8:$G$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,5))</f>
-        <v/>
-      </c>
-      <c r="K24" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,6)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$M$7:$M$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,6),SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$8:$G$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,6))</f>
-        <v/>
-      </c>
-      <c r="L24" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,7)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$M$7:$M$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,7),SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$8:$G$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,7))</f>
-        <v/>
-      </c>
-      <c r="M24" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,8)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$M$7:$M$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,8),SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$8:$G$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,8))</f>
-        <v/>
-      </c>
-      <c r="N24" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,9)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$M$7:$M$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,9),SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$8:$G$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,9))</f>
-        <v/>
-      </c>
-      <c r="O24" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,10)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$M$7:$M$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,10),SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$8:$G$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,10))</f>
-        <v/>
-      </c>
-      <c r="P24" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,11)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$M$7:$M$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,11),SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$8:$G$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,11))</f>
-        <v/>
-      </c>
-      <c r="Q24" s="6">
-        <f>IF(COUNTIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,12)&gt;0,SUMIFS('[Import Monatsdaten.xlsx]Import Monatsdaten'!$M$7:$M$8,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Monatsdaten.xlsx]Import Monatsdaten'!$D$7:$D$8,12),SUMIFS('[D Finanzen.xlsx]D Finanzen'!$G$8:$G$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,12))</f>
-        <v/>
+      <c r="F24" s="6" t="n">
+        <v>-4710.2</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>-3717.47</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>-13169.88</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>-5173.46</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>-2569.29</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="6" t="n">
+        <v>-18831</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>1492.2</v>
+      </c>
+      <c r="N24" s="6" t="n">
+        <v>312223.42</v>
+      </c>
+      <c r="O24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="R24" s="1" t="n"/>
     </row>
@@ -2525,6 +2244,8 @@
       <c r="Q60" s="1" t="n"/>
       <c r="R60" s="1" t="n"/>
     </row>
+    <row r="61"/>
+    <row r="62"/>
     <row r="63">
       <c r="C63" t="inlineStr">
         <is>
